--- a/rules/CORE-000892/negative/01/data/unit-test-coreid-FB4301_negative.xlsx
+++ b/rules/CORE-000892/negative/01/data/unit-test-coreid-FB4301_negative.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cm.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="dm.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dm.xpt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF9EFF9E"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +162,11 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -609,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,6 +652,510 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CMSTDTC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CMSTRF</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CMSTRTPT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CMENRF</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CMENRTPT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CMENDTC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CMSTDTC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CMSTRF</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CMSTRTPT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CMENDTC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CMENRTPT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CMENRF</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DURING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CMSTDTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CMSTRF</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CMSTRTPT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CMENDTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CMENRF</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CMENRTPT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VISIT99</t>
         </is>
       </c>
     </row>
@@ -919,10 +1434,10 @@
           <t>SCREENING</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>2013-04</t>
         </is>
@@ -1123,10 +1638,10 @@
           <t>SCREENING</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>DURING</t>
         </is>
@@ -1206,11 +1721,11 @@
           <t>TREATMENT</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
       <c r="J12" s="10" t="n"/>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>VISIT99</t>
         </is>
@@ -1262,7 +1777,6 @@
     <row r="14">
       <c r="A14" s="10" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="H16" s="13" t="n"/>
     </row>

--- a/rules/CORE-000892/negative/01/data/unit-test-coreid-FB4301_negative.xlsx
+++ b/rules/CORE-000892/negative/01/data/unit-test-coreid-FB4301_negative.xlsx
@@ -47,7 +47,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF9eff9e"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9eff9e"/>
+        <bgColor rgb="FF9eff9e"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -269,6 +275,15 @@
       <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -732,7 +747,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="42" min="1" max="1"/>
@@ -1274,678 +1289,6 @@
         </is>
       </c>
       <c r="F19" s="40" t="inlineStr">
-        <is>
-          <t>VISIT99</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C20" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D20" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" s="44" t="inlineStr">
-        <is>
-          <t>CMSTDTC</t>
-        </is>
-      </c>
-      <c r="F20" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C21" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D21" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" s="44" t="inlineStr">
-        <is>
-          <t>CMSTRF</t>
-        </is>
-      </c>
-      <c r="F21" s="44" t="inlineStr">
-        <is>
-          <t>BEFORE</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C22" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D22" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="44" t="inlineStr">
-        <is>
-          <t>CMSTRTPT</t>
-        </is>
-      </c>
-      <c r="F22" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C23" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D23" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="44" t="inlineStr">
-        <is>
-          <t>CMENRF</t>
-        </is>
-      </c>
-      <c r="F23" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C24" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D24" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="44" t="inlineStr">
-        <is>
-          <t>CMENRTPT</t>
-        </is>
-      </c>
-      <c r="F24" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C25" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D25" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="44" t="inlineStr">
-        <is>
-          <t>CMENDTC</t>
-        </is>
-      </c>
-      <c r="F25" s="44" t="inlineStr">
-        <is>
-          <t>2013-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C26" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D26" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" s="44" t="inlineStr">
-        <is>
-          <t>CMSTDTC</t>
-        </is>
-      </c>
-      <c r="F26" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C27" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D27" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" s="44" t="inlineStr">
-        <is>
-          <t>CMSTRF</t>
-        </is>
-      </c>
-      <c r="F27" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C28" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D28" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="44" t="inlineStr">
-        <is>
-          <t>CMSTRTPT</t>
-        </is>
-      </c>
-      <c r="F28" s="44" t="inlineStr">
-        <is>
-          <t>VISIT 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C29" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D29" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="44" t="inlineStr">
-        <is>
-          <t>CMENRF</t>
-        </is>
-      </c>
-      <c r="F29" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C30" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D30" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" s="44" t="inlineStr">
-        <is>
-          <t>CMENRTPT</t>
-        </is>
-      </c>
-      <c r="F30" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C31" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D31" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="E31" s="44" t="inlineStr">
-        <is>
-          <t>CMENDTC</t>
-        </is>
-      </c>
-      <c r="F31" s="44" t="inlineStr">
-        <is>
-          <t>2013-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B32" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C32" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D32" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="E32" s="44" t="inlineStr">
-        <is>
-          <t>CMSTDTC</t>
-        </is>
-      </c>
-      <c r="F32" s="44" t="inlineStr">
-        <is>
-          <t>2012-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B33" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C33" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D33" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="E33" s="44" t="inlineStr">
-        <is>
-          <t>CMSTRF</t>
-        </is>
-      </c>
-      <c r="F33" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C34" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D34" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="E34" s="44" t="inlineStr">
-        <is>
-          <t>CMSTRTPT</t>
-        </is>
-      </c>
-      <c r="F34" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C35" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D35" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="E35" s="44" t="inlineStr">
-        <is>
-          <t>CMENDTC</t>
-        </is>
-      </c>
-      <c r="F35" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C36" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D36" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="E36" s="44" t="inlineStr">
-        <is>
-          <t>CMENRTPT</t>
-        </is>
-      </c>
-      <c r="F36" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C37" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D37" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="E37" s="44" t="inlineStr">
-        <is>
-          <t>CMENRF</t>
-        </is>
-      </c>
-      <c r="F37" s="44" t="inlineStr">
-        <is>
-          <t>AFTER</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C38" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D38" s="41" t="n">
-        <v>11</v>
-      </c>
-      <c r="E38" s="44" t="inlineStr">
-        <is>
-          <t>CMSTDTC</t>
-        </is>
-      </c>
-      <c r="F38" s="44" t="inlineStr">
-        <is>
-          <t>2013-01-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C39" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D39" s="41" t="n">
-        <v>11</v>
-      </c>
-      <c r="E39" s="44" t="inlineStr">
-        <is>
-          <t>CMSTRF</t>
-        </is>
-      </c>
-      <c r="F39" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C40" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D40" s="41" t="n">
-        <v>11</v>
-      </c>
-      <c r="E40" s="44" t="inlineStr">
-        <is>
-          <t>CMSTRTPT</t>
-        </is>
-      </c>
-      <c r="F40" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B41" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C41" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D41" s="41" t="n">
-        <v>11</v>
-      </c>
-      <c r="E41" s="44" t="inlineStr">
-        <is>
-          <t>CMENDTC</t>
-        </is>
-      </c>
-      <c r="F41" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B42" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C42" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D42" s="41" t="n">
-        <v>11</v>
-      </c>
-      <c r="E42" s="44" t="inlineStr">
-        <is>
-          <t>CMENRF</t>
-        </is>
-      </c>
-      <c r="F42" s="44" t="inlineStr">
-        <is>
-          <t>[ABSENT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B43" s="44" t="inlineStr">
-        <is>
-          <t>cm.xpt</t>
-        </is>
-      </c>
-      <c r="C43" s="44" t="inlineStr">
-        <is>
-          <t>Record</t>
-        </is>
-      </c>
-      <c r="D43" s="41" t="n">
-        <v>11</v>
-      </c>
-      <c r="E43" s="44" t="inlineStr">
-        <is>
-          <t>CMENRTPT</t>
-        </is>
-      </c>
-      <c r="F43" s="44" t="inlineStr">
         <is>
           <t>VISIT99</t>
         </is>
@@ -2283,13 +1626,13 @@
         </is>
       </c>
       <c r="G6" s="36" t="n"/>
-      <c r="H6" s="45" t="inlineStr">
+      <c r="H6" s="46" t="inlineStr">
         <is>
           <t>BEFORE</t>
         </is>
       </c>
       <c r="I6" s="39" t="n"/>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J6" s="47" t="inlineStr">
         <is>
           <t>2013-04</t>
         </is>
@@ -2329,12 +1672,12 @@
       </c>
       <c r="G7" s="36" t="n"/>
       <c r="H7" s="38" t="n"/>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="I7" s="48" t="inlineStr">
         <is>
           <t>VISIT 0</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="47" t="inlineStr">
         <is>
           <t>2013-04</t>
         </is>
@@ -2374,7 +1717,7 @@
           <t>SCREENING</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="47" t="inlineStr">
         <is>
           <t>2012-03</t>
         </is>
@@ -2382,7 +1725,7 @@
       <c r="H8" s="38" t="n"/>
       <c r="I8" s="39" t="n"/>
       <c r="J8" s="36" t="n"/>
-      <c r="K8" s="31" t="inlineStr">
+      <c r="K8" s="48" t="inlineStr">
         <is>
           <t>AFTER</t>
         </is>
@@ -2511,7 +1854,7 @@
           <t>TREATMENT</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="47" t="inlineStr">
         <is>
           <t>2013-01-11</t>
         </is>
@@ -2520,7 +1863,7 @@
       <c r="I11" s="37" t="n"/>
       <c r="J11" s="32" t="n"/>
       <c r="K11" s="37" t="n"/>
-      <c r="L11" s="21" t="inlineStr">
+      <c r="L11" s="47" t="inlineStr">
         <is>
           <t>VISIT99</t>
         </is>
